--- a/data/trans_orig/P70C3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023</t>
+          <t>Población según si le resulta difícil concentrarse en su trabajo debido a sus responsabilidades familiares en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168616</t>
+          <t>168467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185275</t>
+          <t>185288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117800</t>
+          <t>118646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131183</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292817</t>
+          <t>291421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>313334</t>
+          <t>312841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>18969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -1182,97 +1182,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>436</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2247</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2512</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1295,97 +1295,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101690</t>
+          <t>100403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140857</t>
+          <t>141646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74910</t>
+          <t>74276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98008</t>
+          <t>98838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182993</t>
+          <t>181184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231202</t>
+          <t>229895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>20934</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53125</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44626</t>
+          <t>43116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80511</t>
+          <t>78693</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27567</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63578</t>
+          <t>62522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29291</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45651</t>
+          <t>46184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83969</t>
+          <t>82930</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24996</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55190</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>33934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45972</t>
+          <t>45523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81732</t>
+          <t>80713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>16243</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28367</t>
+          <t>27374</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65697</t>
+          <t>65469</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>90195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>56067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74182</t>
+          <t>74809</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>125343</t>
+          <t>127292</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157530</t>
+          <t>157248</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39537</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33967</t>
+          <t>33711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43078</t>
+          <t>42843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67804</t>
+          <t>66434</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>20914</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44523</t>
+          <t>44984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14180</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83590</t>
+          <t>85480</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116957</t>
+          <t>116417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>149944</t>
+          <t>155480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>227199</t>
+          <t>229970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>247093</t>
+          <t>249123</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>348921</t>
+          <t>343543</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>35319</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57068</t>
+          <t>53920</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>34357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>82568</t>
+          <t>84166</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16220</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>27493</t>
+          <t>26151</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>36392</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31134</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>23214</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>46727</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>17240</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>69250</t>
+          <t>68912</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>85815</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>78902</t>
+          <t>79191</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>91447</t>
+          <t>91613</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>151835</t>
+          <t>152800</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>173168</t>
+          <t>173456</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22773</t>
+          <t>23786</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>320</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4475,97 +4475,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>39661</t>
+          <t>39379</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>61516</t>
+          <t>60706</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>33873</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>49888</t>
+          <t>50089</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>78891</t>
+          <t>78424</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>105032</t>
+          <t>105113</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>30089</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23275</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>29522</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>48672</t>
+          <t>48691</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23512</t>
+          <t>22881</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>35559</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>32400</t>
+          <t>32552</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>52777</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>21382</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>27041</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>191414</t>
+          <t>190447</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>234032</t>
+          <t>234231</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>184004</t>
+          <t>185873</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>213994</t>
+          <t>215525</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>385629</t>
+          <t>387419</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>436724</t>
+          <t>439099</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>56854</t>
+          <t>57352</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>96544</t>
+          <t>99825</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>48615</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>72894</t>
+          <t>73149</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>114434</t>
+          <t>114108</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>161862</t>
+          <t>162545</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>23267</t>
+          <t>23989</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>47406</t>
+          <t>48758</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>30138</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>22218</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>24918</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>47362</t>
+          <t>48394</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>18772</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>343339</t>
+          <t>348721</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>566944</t>
+          <t>566394</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>105518</t>
+          <t>105606</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>135069</t>
+          <t>135181</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>453372</t>
+          <t>454898</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>744913</t>
+          <t>749603</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>43890</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>208584</t>
+          <t>206332</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>77493</t>
+          <t>76332</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>105494</t>
+          <t>106077</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>103940</t>
+          <t>98541</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>300069</t>
+          <t>301069</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>7361</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>43552</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>45887</t>
+          <t>45700</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>84526</t>
+          <t>84340</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>31658</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>28460</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>27498</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1100609</t>
+          <t>1096775</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1464224</t>
+          <t>1490859</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>787801</t>
+          <t>793114</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>948443</t>
+          <t>932006</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1918805</t>
+          <t>1914075</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2339860</t>
+          <t>2376111</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>246621</t>
+          <t>246584</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>459577</t>
+          <t>459871</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>293351</t>
+          <t>295082</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>384547</t>
+          <t>382589</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>588144</t>
+          <t>570082</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>826312</t>
+          <t>827734</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>97115</t>
+          <t>94785</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>176428</t>
+          <t>176221</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>87040</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>128919</t>
+          <t>125268</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>199122</t>
+          <t>190239</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>289608</t>
+          <t>286151</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>79429</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>154573</t>
+          <t>152722</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>72518</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>107340</t>
+          <t>106799</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>167488</t>
+          <t>159040</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>248300</t>
+          <t>245454</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>40309</t>
+          <t>37659</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>84900</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>38448</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>66176</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>88447</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>139554</t>
+          <t>141313</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>44316</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>48413</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>39451</t>
+          <t>40783</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>76903</t>
+          <t>77691</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70C3_2023-Provincia-trans_orig.xlsx
@@ -725,17 +725,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>178749</t>
+          <t>186208</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>168467</t>
+          <t>176057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185288</t>
+          <t>192234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>125568</t>
+          <t>134226</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118646</t>
+          <t>127932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>140063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>304317</t>
+          <t>320434</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>291421</t>
+          <t>308833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>312841</t>
+          <t>329359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19649</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30336</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>827</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>468</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>468</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>121177</t>
+          <t>128074</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100403</t>
+          <t>110113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141646</t>
+          <t>149490</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86474</t>
+          <t>90982</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74276</t>
+          <t>78247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98838</t>
+          <t>102966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>207651</t>
+          <t>219056</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181184</t>
+          <t>193821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>229895</t>
+          <t>241191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -1633,102 +1633,102 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34411</t>
+          <t>34362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51447</t>
+          <t>49887</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19,44%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>26124</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19086</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>36582</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>60486</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>44316</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>79644</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>13,95%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20,85%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>24579</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17168</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35673</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>10,22%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>58990</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>43116</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>78693</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42685</t>
+          <t>44542</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62522</t>
+          <t>63382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>62874</t>
+          <t>65257</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46184</t>
+          <t>48065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82930</t>
+          <t>85319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38163</t>
+          <t>38664</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24367</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>33417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>61177</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45523</t>
+          <t>46014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80713</t>
+          <t>82796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16243</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>17192</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27374</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246741</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>176952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414810</t>
+          <t>433520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77247</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65469</t>
+          <t>64864</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90195</t>
+          <t>90738</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>66818</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56067</t>
+          <t>57309</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74809</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142436</t>
+          <t>145469</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>127292</t>
+          <t>130069</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>157248</t>
+          <t>160800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>29379</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40603</t>
+          <t>39969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33711</t>
+          <t>33918</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>54515</t>
+          <t>54496</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42843</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66434</t>
+          <t>67367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19513</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28733</t>
+          <t>28191</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21593</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,17 +2611,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>33199</t>
+          <t>33573</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>24177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>45210</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>14558</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>27911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>120315</t>
+          <t>122469</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120315</t>
+          <t>122469</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>120315</t>
+          <t>122469</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>268997</t>
+          <t>272080</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>268997</t>
+          <t>272080</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>268997</t>
+          <t>272080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>101881</t>
+          <t>126832</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85480</t>
+          <t>108079</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116417</t>
+          <t>147320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>191609</t>
+          <t>105837</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155480</t>
+          <t>92593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>229970</t>
+          <t>118699</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>293490</t>
+          <t>232669</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>249123</t>
+          <t>206486</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>343543</t>
+          <t>254074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23637</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>22339</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35319</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>37610</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14936</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53920</t>
+          <t>51348</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>57947</t>
+          <t>70626</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84166</t>
+          <t>88448</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15487</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>12755</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>35825</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>30095</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>22635</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>12904</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>40409</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>33924</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>25230</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46727</t>
+          <t>50874</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>168662</t>
+          <t>213024</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>168662</t>
+          <t>213024</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>168662</t>
+          <t>213024</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>257669</t>
+          <t>179904</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>257669</t>
+          <t>179904</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>257669</t>
+          <t>179904</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>426330</t>
+          <t>392928</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>426330</t>
+          <t>392928</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>426330</t>
+          <t>392928</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>40655</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>77646</t>
+          <t>92346</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>68912</t>
+          <t>81658</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>85815</t>
+          <t>101970</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>85959</t>
+          <t>94660</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>79191</t>
+          <t>86849</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>91613</t>
+          <t>100642</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>163605</t>
+          <t>187006</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>152800</t>
+          <t>174646</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>173456</t>
+          <t>198853</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>77,8%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>12018</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>21110</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,67 +4166,67 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>18542</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>12416</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>26045</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
           <t>7,25%</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>16470</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>11457</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>23786</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>455</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>50181</t>
+          <t>51955</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>39379</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>60706</t>
+          <t>62876</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>42647</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>34577</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>50089</t>
+          <t>50227</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>92209</t>
+          <t>94603</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>78424</t>
+          <t>80933</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>105113</t>
+          <t>107722</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>13733</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>29595</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>38211</t>
+          <t>37789</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>29522</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>48691</t>
+          <t>47628</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>24660</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,22 +4996,22 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14237</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30021</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>26073</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>35559</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>41681</t>
+          <t>41877</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>32552</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>52777</t>
+          <t>53531</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20942</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>27041</t>
+          <t>28202</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>996</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>214475</t>
+          <t>248456</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>190447</t>
+          <t>225458</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>234231</t>
+          <t>268541</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>199694</t>
+          <t>234308</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>185873</t>
+          <t>217133</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>215525</t>
+          <t>249969</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>414169</t>
+          <t>482765</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>387419</t>
+          <t>458081</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>439099</t>
+          <t>509864</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>74410</t>
+          <t>86771</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>57352</t>
+          <t>70262</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>108601</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>72295</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>48615</t>
+          <t>58714</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>73149</t>
+          <t>88238</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>134662</t>
+          <t>159067</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>114108</t>
+          <t>135229</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>162545</t>
+          <t>183658</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>29598</t>
+          <t>34118</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>35086</t>
+          <t>39469</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>26178</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>48758</t>
+          <t>51296</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>20448</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>30819</t>
+          <t>32552</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,22 +5904,22 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>34595</t>
+          <t>39682</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>48394</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>15533</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -6060,69 +6060,69 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>6195</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>12113</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>5925</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>11696</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>334301</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>307574</t>
+          <t>363661</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>307574</t>
+          <t>363661</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>307574</t>
+          <t>363661</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>641875</t>
+          <t>751176</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>641875</t>
+          <t>751176</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>641875</t>
+          <t>751176</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>461729</t>
+          <t>257709</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>348721</t>
+          <t>234271</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>566394</t>
+          <t>278357</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>119862</t>
+          <t>141082</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>105606</t>
+          <t>125045</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>135181</t>
+          <t>157650</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>581591</t>
+          <t>398791</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>454898</t>
+          <t>370293</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>749603</t>
+          <t>424564</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>121799</t>
+          <t>141389</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>43890</t>
+          <t>122420</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>206332</t>
+          <t>163351</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>90862</t>
+          <t>105439</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>76332</t>
+          <t>90176</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>106077</t>
+          <t>120031</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>212661</t>
+          <t>246828</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>98541</t>
+          <t>221033</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>301069</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>41314</t>
+          <t>42913</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>41937</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>26371</t>
+          <t>31868</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>45700</t>
+          <t>53191</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>57630</t>
+          <t>71913</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>57573</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>84340</t>
+          <t>89043</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>17058</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>19363</t>
+          <t>22403</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>28460</t>
+          <t>30317</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>14208</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7085,32 +7085,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1220717</t>
+          <t>1096283</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1096775</t>
+          <t>1043277</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1490859</t>
+          <t>1143020</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7120,32 +7120,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>841435</t>
+          <t>828102</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>793114</t>
+          <t>794624</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>932006</t>
+          <t>863214</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>2062152</t>
+          <t>1924384</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1914075</t>
+          <t>1855821</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2376111</t>
+          <t>1985658</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -7198,32 +7198,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>390512</t>
+          <t>447746</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>246584</t>
+          <t>410939</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>459871</t>
+          <t>489286</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7233,32 +7233,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>349728</t>
+          <t>389018</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>295082</t>
+          <t>359376</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>382589</t>
+          <t>422537</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>740240</t>
+          <t>836764</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>570082</t>
+          <t>785447</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>827734</t>
+          <t>885705</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -7311,32 +7311,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>142323</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>133456</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>176221</t>
+          <t>188963</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7346,32 +7346,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>118216</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>87040</t>
+          <t>100326</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>125268</t>
+          <t>137841</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>248813</t>
+          <t>277500</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>190239</t>
+          <t>245777</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>286151</t>
+          <t>311375</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -7424,32 +7424,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>123297</t>
+          <t>129543</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>106890</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>152722</t>
+          <t>156416</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7459,32 +7459,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>87922</t>
+          <t>96593</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>80090</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>106799</t>
+          <t>114341</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>211219</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>159040</t>
+          <t>197936</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>245454</t>
+          <t>260345</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -7537,32 +7537,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>63084</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>89230</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7572,32 +7572,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>51755</t>
+          <t>60954</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>38273</t>
+          <t>46855</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>66176</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>114840</t>
+          <t>128485</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>88447</t>
+          <t>108059</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>141313</t>
+          <t>155142</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -7650,32 +7650,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>50953</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7685,32 +7685,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>26159</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>31673</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>58613</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>45805</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>77691</t>
+          <t>76991</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7763,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1970211</t>
+          <t>1936200</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1463489</t>
+          <t>1515683</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3433701</t>
+          <t>3451883</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
